--- a/artfynd/A 44389-2021 artfynd.xlsx
+++ b/artfynd/A 44389-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44389-2021 artfynd.xlsx
+++ b/artfynd/A 44389-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78213712</v>
+        <v>78213709</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505209.201257985</v>
+        <v>505219</v>
       </c>
       <c r="R2" t="n">
-        <v>6585191.362350711</v>
+        <v>6585161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,24 +757,14 @@
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>51 bladrosetter</t>
+          <t>300 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -814,12 +799,7 @@
         <v>78213711</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505209.2152941108</v>
+        <v>505209</v>
       </c>
       <c r="R3" t="n">
-        <v>6585181.179636937</v>
+        <v>6585181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,19 +878,9 @@
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-05-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -947,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78213709</v>
+        <v>78213712</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1001,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505219.4432228661</v>
+        <v>505209</v>
       </c>
       <c r="R4" t="n">
-        <v>6585161.337340889</v>
+        <v>6585191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,24 +999,14 @@
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>300 bladrosetter</t>
+          <t>51 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1086,12 +1041,7 @@
         <v>90041772</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505211.7724417816</v>
+        <v>505212</v>
       </c>
       <c r="R5" t="n">
-        <v>6585176.091785817</v>
+        <v>6585176</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1173,19 +1123,9 @@
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-05-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 44389-2021 artfynd.xlsx
+++ b/artfynd/A 44389-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78213709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78213711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78213712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,8 +1184,19 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90041772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>